--- a/python/배차표.xlsx
+++ b/python/배차표.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH213"/>
+  <dimension ref="A1:AK213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -820,6 +820,21 @@
         <f>AF2+AG2</f>
         <v/>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>서울71사1519</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -937,6 +952,21 @@
         <f>AF3+AG3</f>
         <v/>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>서울74사5232</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1057,6 +1087,21 @@
       <c r="AH4" s="9">
         <f>AF4+AG4</f>
         <v/>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>서울74사7412</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1175,6 +1220,21 @@
         <f>AF5+AG5</f>
         <v/>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>서울71사1560</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1312,6 +1372,21 @@
         <f>AF6+AG6</f>
         <v/>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>서울71사1529</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1437,6 +1512,21 @@
         <f>AF7+AG7</f>
         <v/>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>서울71사1529</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1570,6 +1660,21 @@
         <f>AF8+AG8</f>
         <v/>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>서울71사1530</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1694,6 +1799,21 @@
       <c r="AH9" s="9">
         <f>AF9+AG9</f>
         <v/>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>서울71사1457</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1812,6 +1932,21 @@
         <f>AF10+AG10</f>
         <v/>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>서울71사1553</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1933,6 +2068,21 @@
         <f>AF11+AG11</f>
         <v/>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>서울71사1584</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2054,6 +2204,21 @@
         <f>AF12+AG12</f>
         <v/>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>서울71사1584</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2191,6 +2356,21 @@
         <f>AF13+AG13</f>
         <v/>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>서울71사1587</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2315,6 +2495,21 @@
       <c r="AH14" s="9">
         <f>AF14+AG14</f>
         <v/>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>서울74사5182</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2429,6 +2624,21 @@
         <f>AF15+AG15</f>
         <v/>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>서울71사1553</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2565,6 +2775,21 @@
       <c r="AH16" s="9">
         <f>AF16+AG16</f>
         <v/>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>서울74사6068</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -2699,6 +2924,21 @@
         <f>AF17+AG17</f>
         <v/>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>서울74사5183</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2828,6 +3068,21 @@
         <f>AF18+AG18</f>
         <v/>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>서울71사1522</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2957,6 +3212,21 @@
         <f>AF19+AG19</f>
         <v/>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>서울71사1519</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -3082,6 +3352,21 @@
         <f>AF20+AG20</f>
         <v/>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>서울71사1526</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -3207,6 +3492,21 @@
         <f>AF21+AG21</f>
         <v/>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>서울71사1444</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -3336,6 +3636,21 @@
         <f>AF22+AG22</f>
         <v/>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>서울71사1444</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -3469,6 +3784,21 @@
         <f>AF23+AG23</f>
         <v/>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>서울71사1450</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -3594,6 +3924,21 @@
         <f>AF24+AG24</f>
         <v/>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>서울71사1450</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -3719,6 +4064,21 @@
         <f>AF25+AG25</f>
         <v/>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>서울71사1457</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -3848,6 +4208,21 @@
         <f>AF26+AG26</f>
         <v/>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>서울71사1497</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3977,6 +4352,21 @@
         <f>AF27+AG27</f>
         <v/>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>서울71사1550</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -4098,6 +4488,21 @@
         <f>AF28+AG28</f>
         <v/>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>서울71사1552</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -4227,6 +4632,21 @@
         <f>AF29+AG29</f>
         <v/>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>서울71사1522</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -4360,6 +4780,21 @@
         <f>AF30+AG30</f>
         <v/>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>서울74사5211</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -4492,6 +4927,21 @@
       <c r="AH31" s="9">
         <f>AF31+AG31</f>
         <v/>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>서울71사1526</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -4622,6 +5072,21 @@
         <f>AF32+AG32</f>
         <v/>
       </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>서울71사1527</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -4747,6 +5212,21 @@
         <f>AF33+AG33</f>
         <v/>
       </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>서울71사1525</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -4875,6 +5355,21 @@
       <c r="AH34" s="9">
         <f>AF34+AG34</f>
         <v/>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>서울74사7412</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -5009,6 +5504,21 @@
         <f>AF35+AG35</f>
         <v/>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>서울74사7427</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -5138,6 +5648,21 @@
         <f>AF36+AG36</f>
         <v/>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>서울71사1447</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -5275,6 +5800,21 @@
         <f>AF37+AG37</f>
         <v/>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>서울71사1514</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -5411,6 +5951,21 @@
       <c r="AH38" s="9">
         <f>AF38+AG38</f>
         <v/>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>서울74사5182</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -5529,6 +6084,21 @@
         <f>AF39+AG39</f>
         <v/>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>서울71사1527</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -5642,6 +6212,21 @@
         <f>AF40+AG40</f>
         <v/>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>서울71사1485</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -5766,6 +6351,21 @@
       <c r="AH41" s="9">
         <f>AF41+AG41</f>
         <v/>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>서울74사6068</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -5876,6 +6476,21 @@
         <f>AF42+AG42</f>
         <v/>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>서울71사1484</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -6001,6 +6616,21 @@
         <f>AF43+AG43</f>
         <v/>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>서울71사1500</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -6130,6 +6760,21 @@
         <f>AF44+AG44</f>
         <v/>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>서울71사1485</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -6255,6 +6900,21 @@
         <f>AF45+AG45</f>
         <v/>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>서울71사1483</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -6391,6 +7051,21 @@
       <c r="AH46" s="9">
         <f>AF46+AG46</f>
         <v/>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>서울71사1501</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -6509,6 +7184,21 @@
         <f>AF47+AG47</f>
         <v/>
       </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>서울71사1502</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -6634,6 +7324,21 @@
         <f>AF48+AG48</f>
         <v/>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>서울71사1514</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -6762,6 +7467,21 @@
       <c r="AH49" s="9">
         <f>AF49+AG49</f>
         <v/>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>서울71사1555</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -6888,6 +7608,21 @@
         <f>AF50+AG50</f>
         <v/>
       </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>서울71사1502</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -7013,6 +7748,21 @@
         <f>AF51+AG51</f>
         <v/>
       </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>서울71사1513</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -7137,6 +7887,21 @@
       <c r="AH52" s="9">
         <f>AF52+AG52</f>
         <v/>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>서울74사5211</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -7255,6 +8020,21 @@
         <f>AF53+AG53</f>
         <v/>
       </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>서울74사5183</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -7379,6 +8159,21 @@
       <c r="AH54" s="9">
         <f>AF54+AG54</f>
         <v/>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>서울71사1516</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -7513,6 +8308,21 @@
         <f>AF55+AG55</f>
         <v/>
       </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>서울71사1534</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -7638,6 +8448,21 @@
         <f>AF56+AG56</f>
         <v/>
       </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>서울71사1501</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -7763,6 +8588,21 @@
         <f>AF57+AG57</f>
         <v/>
       </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>서울71사1506</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -7888,6 +8728,21 @@
         <f>AF58+AG58</f>
         <v/>
       </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>서울71사1518</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -8009,6 +8864,21 @@
         <f>AF59+AG59</f>
         <v/>
       </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>서울71사1518</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -8130,6 +9000,21 @@
         <f>AF60+AG60</f>
         <v/>
       </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>서울71사1520</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -8250,6 +9135,21 @@
       <c r="AH61" s="9">
         <f>AF61+AG61</f>
         <v/>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>서울71사1520</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -8380,6 +9280,21 @@
         <f>AF62+AG62</f>
         <v/>
       </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>서울71사1524</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -8504,6 +9419,21 @@
       <c r="AH63" s="9">
         <f>AF63+AG63</f>
         <v/>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>서울71사1560</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -8629,6 +9559,21 @@
       <c r="AH64" s="9">
         <f>AF64+AG64</f>
         <v/>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>서울71사1463</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -8747,6 +9692,21 @@
         <f>AF65+AG65</f>
         <v/>
       </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>서울71사1524</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -8863,6 +9823,21 @@
       <c r="AH66" s="9">
         <f>AF66+AG66</f>
         <v/>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>서울71사1533</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -8989,6 +9964,21 @@
         <f>AF67+AG67</f>
         <v/>
       </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>서울71사1534</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -9113,6 +10103,21 @@
       <c r="AH68" s="9">
         <f>AF68+AG68</f>
         <v/>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>서울71사1530</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -9231,6 +10236,21 @@
         <f>AF69+AG69</f>
         <v/>
       </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>서울71사1503</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -9352,6 +10372,21 @@
         <f>AF70+AG70</f>
         <v/>
       </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>서울71사1503</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -9477,6 +10512,21 @@
         <f>AF71+AG71</f>
         <v/>
       </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>서울71사1505</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -9610,6 +10660,21 @@
         <f>AF72+AG72</f>
         <v/>
       </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>서울71사1533</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -9735,6 +10800,21 @@
         <f>AF73+AG73</f>
         <v/>
       </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>서울71사1443</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -9860,6 +10940,21 @@
         <f>AF74+AG74</f>
         <v/>
       </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>서울71사1443</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -9985,6 +11080,21 @@
         <f>AF75+AG75</f>
         <v/>
       </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>서울71사1461</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -10090,6 +11200,21 @@
         <f>AF76+AG76</f>
         <v/>
       </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>서울71사1462</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -10222,6 +11347,21 @@
       <c r="AH77" s="9">
         <f>AF77+AG77</f>
         <v/>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>서울71사1462</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -10344,6 +11484,21 @@
         <f>AF78+AG78</f>
         <v/>
       </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>서울71사1463</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -10457,6 +11612,21 @@
         <f>AF79+AG79</f>
         <v/>
       </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>서울71사1481</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -10582,6 +11752,21 @@
         <f>AF80+AG80</f>
         <v/>
       </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>서울71사1481</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -10707,6 +11892,21 @@
         <f>AF81+AG81</f>
         <v/>
       </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>서울71사1483</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -10832,6 +12032,21 @@
         <f>AF82+AG82</f>
         <v/>
       </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>서울71사1505</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -10957,6 +12172,21 @@
         <f>AF83+AG83</f>
         <v/>
       </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>서울71사1516</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -11082,6 +12312,21 @@
         <f>AF84+AG84</f>
         <v/>
       </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>서울71사1484</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -11203,6 +12448,21 @@
         <f>AF85+AG85</f>
         <v/>
       </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>서울71사1500</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -11324,6 +12584,21 @@
         <f>AF86+AG86</f>
         <v/>
       </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>서울71사1537</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -11453,6 +12728,21 @@
         <f>AF87+AG87</f>
         <v/>
       </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>서울74사5207</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>2021-12-27</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -11578,6 +12868,21 @@
         <f>AF88+AG88</f>
         <v/>
       </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>서울74사5202</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -11699,6 +13004,21 @@
         <f>AF89+AG89</f>
         <v/>
       </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>서울74사5207</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>2021-12-27</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -11836,6 +13156,21 @@
         <f>AF90+AG90</f>
         <v/>
       </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>서울74사5159</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>2021-12-08</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -11961,6 +13296,21 @@
         <f>AF91+AG91</f>
         <v/>
       </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>서울74사5159</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>2021-12-08</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -12082,6 +13432,21 @@
         <f>AF92+AG92</f>
         <v/>
       </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>서울71사1544</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -12203,6 +13568,21 @@
         <f>AF93+AG93</f>
         <v/>
       </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>서울74사5152</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -12328,6 +13708,21 @@
         <f>AF94+AG94</f>
         <v/>
       </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>서울71사1546</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -12460,6 +13855,21 @@
       <c r="AH95" s="9">
         <f>AF95+AG95</f>
         <v/>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>서울74사5249</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -12574,6 +13984,17 @@
         <f>AF96+AG96</f>
         <v/>
       </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -12699,6 +14120,21 @@
         <f>AF97+AG97</f>
         <v/>
       </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>서울71사1549</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -12824,6 +14260,21 @@
         <f>AF98+AG98</f>
         <v/>
       </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>서울71사1535</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -12953,6 +14404,21 @@
         <f>AF99+AG99</f>
         <v/>
       </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>서울71사1535</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -13078,6 +14544,21 @@
         <f>AF100+AG100</f>
         <v/>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>서울71사1536</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -13202,6 +14683,21 @@
       <c r="AH101" s="9">
         <f>AF101+AG101</f>
         <v/>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>서울71사1536</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -13312,6 +14808,21 @@
         <f>AF102+AG102</f>
         <v/>
       </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>서울74사5201</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -13429,6 +14940,21 @@
         <f>AF103+AG103</f>
         <v/>
       </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>서울71사1538</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -13550,6 +15076,21 @@
         <f>AF104+AG104</f>
         <v/>
       </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>서울71사1538</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -13687,6 +15228,21 @@
         <f>AF105+AG105</f>
         <v/>
       </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>서울71사1542</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -13823,6 +15379,21 @@
       <c r="AH106" s="9">
         <f>AF106+AG106</f>
         <v/>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>서울71사1546</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -13941,6 +15512,21 @@
         <f>AF107+AG107</f>
         <v/>
       </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>서울71사1547</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -14066,6 +15652,21 @@
         <f>AF108+AG108</f>
         <v/>
       </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>서울71사1547</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -14191,6 +15792,21 @@
         <f>AF109+AG109</f>
         <v/>
       </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>서울71사1542</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -14320,6 +15936,21 @@
         <f>AF110+AG110</f>
         <v/>
       </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>서울71사1543</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -14440,6 +16071,21 @@
       <c r="AH111" s="9">
         <f>AF111+AG111</f>
         <v/>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>서울71사1543</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -14554,6 +16200,17 @@
         <f>AF112+AG112</f>
         <v/>
       </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -14679,6 +16336,21 @@
         <f>AF113+AG113</f>
         <v/>
       </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>서울74사5170</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -14804,6 +16476,21 @@
         <f>AF114+AG114</f>
         <v/>
       </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>서울74사5170</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -14924,6 +16611,21 @@
       <c r="AH115" s="9">
         <f>AF115+AG115</f>
         <v/>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>서울71사1544</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -15049,6 +16751,21 @@
       <c r="AH116" s="9">
         <f>AF116+AG116</f>
         <v/>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>서울74사5250</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -15107,6 +16824,21 @@
         <f>AF117+AG117</f>
         <v/>
       </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>서울74사5250</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -15236,6 +16968,21 @@
         <f>AF118+AG118</f>
         <v/>
       </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>서울74사5152</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -15360,6 +17107,21 @@
       <c r="AH119" s="9">
         <f>AF119+AG119</f>
         <v/>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>서울74사5249</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -15466,6 +17228,21 @@
         <f>AF120+AG120</f>
         <v/>
       </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>서울71사1549</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -15583,6 +17360,21 @@
         <f>AF121+AG121</f>
         <v/>
       </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>서울74사5198</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -15703,6 +17495,21 @@
       <c r="AH122" s="9">
         <f>AF122+AG122</f>
         <v/>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>서울74사5198</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -15761,6 +17568,21 @@
         <f>AF123+AG123</f>
         <v/>
       </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>서울71사1561</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -15878,6 +17700,21 @@
         <f>AF124+AG124</f>
         <v/>
       </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>서울71사1545</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -15999,6 +17836,21 @@
         <f>AF125+AG125</f>
         <v/>
       </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>서울74사5248</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -16124,6 +17976,21 @@
         <f>AF126+AG126</f>
         <v/>
       </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>서울74사5248</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -16249,6 +18116,21 @@
         <f>AF127+AG127</f>
         <v/>
       </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>서울74사5156</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -16386,6 +18268,21 @@
         <f>AF128+AG128</f>
         <v/>
       </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>서울74사5156</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -16522,6 +18419,21 @@
       <c r="AH129" s="9">
         <f>AF129+AG129</f>
         <v/>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>서울71사1561</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -16640,6 +18552,21 @@
         <f>AF130+AG130</f>
         <v/>
       </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>서울74사5201</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -16765,6 +18692,21 @@
         <f>AF131+AG131</f>
         <v/>
       </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>서울71사1545</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -16885,6 +18827,21 @@
       <c r="AH132" s="9">
         <f>AF132+AG132</f>
         <v/>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>서울71사1586</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -17003,6 +18960,21 @@
         <f>AF133+AG133</f>
         <v/>
       </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>서울71사1563</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -17128,6 +19100,21 @@
         <f>AF134+AG134</f>
         <v/>
       </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>서울71사1563</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -17253,6 +19240,21 @@
         <f>AF135+AG135</f>
         <v/>
       </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>서울71사1564</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -17374,6 +19376,21 @@
         <f>AF136+AG136</f>
         <v/>
       </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>서울71사1586</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -17494,6 +19511,21 @@
       <c r="AH137" s="9">
         <f>AF137+AG137</f>
         <v/>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>서울71사1564</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -17620,6 +19652,17 @@
         <f>AF138+AG138</f>
         <v/>
       </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr"/>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -17733,6 +19776,17 @@
         <f>AF139+AG139</f>
         <v/>
       </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr"/>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -17850,6 +19904,17 @@
         <f>AF140+AG140</f>
         <v/>
       </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr"/>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -17963,6 +20028,17 @@
         <f>AF141+AG141</f>
         <v/>
       </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr"/>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -18072,6 +20148,17 @@
         <f>AF142+AG142</f>
         <v/>
       </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr"/>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -18189,6 +20276,17 @@
         <f>AF143+AG143</f>
         <v/>
       </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr"/>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -18306,6 +20404,17 @@
         <f>AF144+AG144</f>
         <v/>
       </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr"/>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -18426,6 +20535,17 @@
       <c r="AH145" s="9">
         <f>AF145+AG145</f>
         <v/>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr"/>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -18484,6 +20604,17 @@
         <f>AF146+AG146</f>
         <v/>
       </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr"/>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -18597,6 +20728,17 @@
         <f>AF147+AG147</f>
         <v/>
       </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr"/>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -18710,6 +20852,17 @@
         <f>AF148+AG148</f>
         <v/>
       </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr"/>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -18831,6 +20984,17 @@
         <f>AF149+AG149</f>
         <v/>
       </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr"/>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -18948,6 +21112,17 @@
         <f>AF150+AG150</f>
         <v/>
       </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr"/>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -19073,6 +21248,17 @@
         <f>AF151+AG151</f>
         <v/>
       </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr"/>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -19186,6 +21372,17 @@
         <f>AF152+AG152</f>
         <v/>
       </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr"/>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -19307,6 +21504,17 @@
         <f>AF153+AG153</f>
         <v/>
       </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr"/>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -19416,6 +21624,17 @@
         <f>AF154+AG154</f>
         <v/>
       </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr"/>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -19541,6 +21760,17 @@
         <f>AF155+AG155</f>
         <v/>
       </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr"/>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -19650,6 +21880,17 @@
         <f>AF156+AG156</f>
         <v/>
       </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr"/>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -19771,6 +22012,17 @@
         <f>AF157+AG157</f>
         <v/>
       </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr"/>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -19880,6 +22132,17 @@
         <f>AF158+AG158</f>
         <v/>
       </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr"/>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -19997,6 +22260,17 @@
         <f>AF159+AG159</f>
         <v/>
       </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr"/>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -20106,6 +22380,17 @@
         <f>AF160+AG160</f>
         <v/>
       </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr"/>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -20226,6 +22511,17 @@
       <c r="AH161" s="9">
         <f>AF161+AG161</f>
         <v/>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr"/>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -20339,6 +22635,17 @@
       <c r="AH162" s="9">
         <f>AF162+AG162</f>
         <v/>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr"/>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -20449,6 +22756,17 @@
         <f>AF163+AG163</f>
         <v/>
       </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr"/>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -20566,6 +22884,17 @@
         <f>AF164+AG164</f>
         <v/>
       </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr"/>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -20683,6 +23012,17 @@
         <f>AF165+AG165</f>
         <v/>
       </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr"/>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -20800,6 +23140,17 @@
         <f>AF166+AG166</f>
         <v/>
       </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr"/>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -20905,6 +23256,17 @@
         <f>AF167+AG167</f>
         <v/>
       </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr"/>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -21021,6 +23383,17 @@
       <c r="AH168" s="9">
         <f>AF168+AG168</f>
         <v/>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr"/>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -21138,6 +23511,17 @@
       <c r="AH169" s="9">
         <f>AF169+AG169</f>
         <v/>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr"/>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -21240,6 +23624,17 @@
         <f>AF170+AG170</f>
         <v/>
       </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr"/>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -21360,6 +23755,17 @@
       <c r="AH171" s="9">
         <f>AF171+AG171</f>
         <v/>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr"/>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -21474,6 +23880,17 @@
         <f>AF172+AG172</f>
         <v/>
       </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr"/>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -21591,6 +24008,17 @@
         <f>AF173+AG173</f>
         <v/>
       </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr"/>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -21707,6 +24135,17 @@
       <c r="AH174" s="9">
         <f>AF174+AG174</f>
         <v/>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr"/>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -21817,6 +24256,17 @@
         <f>AF175+AG175</f>
         <v/>
       </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr"/>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -21942,6 +24392,17 @@
         <f>AF176+AG176</f>
         <v/>
       </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr"/>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -22059,6 +24520,17 @@
         <f>AF177+AG177</f>
         <v/>
       </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr"/>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -22176,6 +24648,17 @@
         <f>AF178+AG178</f>
         <v/>
       </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr"/>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -22288,6 +24771,17 @@
       <c r="AH179" s="9">
         <f>AF179+AG179</f>
         <v/>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr"/>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -22394,6 +24888,17 @@
         <f>AF180+AG180</f>
         <v/>
       </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr"/>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -22503,6 +25008,17 @@
         <f>AF181+AG181</f>
         <v/>
       </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr"/>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -22624,6 +25140,17 @@
         <f>AF182+AG182</f>
         <v/>
       </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr"/>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -22744,6 +25271,17 @@
       <c r="AH183" s="9">
         <f>AF183+AG183</f>
         <v/>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr"/>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -22862,6 +25400,17 @@
         <f>AF184+AG184</f>
         <v/>
       </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr"/>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -22986,6 +25535,17 @@
       <c r="AH185" s="9">
         <f>AF185+AG185</f>
         <v/>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr"/>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -23108,6 +25668,17 @@
         <f>AF186+AG186</f>
         <v/>
       </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr"/>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -23229,6 +25800,17 @@
         <f>AF187+AG187</f>
         <v/>
       </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr"/>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -23350,6 +25932,17 @@
         <f>AF188+AG188</f>
         <v/>
       </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr"/>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -23475,6 +26068,17 @@
         <f>AF189+AG189</f>
         <v/>
       </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr"/>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -23592,6 +26196,17 @@
         <f>AF190+AG190</f>
         <v/>
       </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr"/>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -23713,6 +26328,17 @@
         <f>AF191+AG191</f>
         <v/>
       </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr"/>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -23829,6 +26455,17 @@
       <c r="AH192" s="9">
         <f>AF192+AG192</f>
         <v/>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr"/>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -23935,6 +26572,17 @@
         <f>AF193+AG193</f>
         <v/>
       </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr"/>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -24051,6 +26699,17 @@
       <c r="AH194" s="9">
         <f>AF194+AG194</f>
         <v/>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr"/>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -24160,6 +26819,17 @@
       <c r="AH195" s="9">
         <f>AF195+AG195</f>
         <v/>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr"/>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -24242,6 +26912,17 @@
         <f>AF196+AG196</f>
         <v/>
       </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr"/>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -24322,6 +27003,17 @@
       <c r="AH197" s="9">
         <f>AF197+AG197</f>
         <v/>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr"/>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -24763,6 +27455,21 @@
         <f>AF201+AG201</f>
         <v/>
       </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>서울74사5232</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -24981,6 +27688,21 @@
         <f>AF203+AG203</f>
         <v/>
       </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>서울71사1492</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -25191,6 +27913,21 @@
         <f>AF205+AG205</f>
         <v/>
       </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>서울71사1513</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -25320,6 +28057,21 @@
         <f>AF206+AG206</f>
         <v/>
       </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>5413</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>서울71사1537</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -25456,6 +28208,21 @@
       <c r="AH207" s="9">
         <f>AF207+AG207</f>
         <v/>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>서울71사1525</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -25578,6 +28345,17 @@
         <f>AF208+AG208</f>
         <v/>
       </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr"/>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -25707,6 +28485,21 @@
         <f>AF209+AG209</f>
         <v/>
       </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>서울71사1492</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -25831,6 +28624,21 @@
       <c r="AH210" s="9">
         <f>AF210+AG210</f>
         <v/>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>서울71사1587</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -25917,6 +28725,21 @@
         <f>AF211+AG211</f>
         <v/>
       </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>서울71사1523</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
@@ -26006,6 +28829,21 @@
         <f>AF212+AG212</f>
         <v/>
       </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>서울71사1511</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -26119,6 +28957,17 @@
         <f>AF213+AG213</f>
         <v/>
       </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>예비본사</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr"/>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
